--- a/excel/bag_comparison.xlsx
+++ b/excel/bag_comparison.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="เปรียบเทียบ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ขนาด (ตัวเลข)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ข้อมูลประกอบข้อเสนอ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -83,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -105,11 +106,44 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -167,6 +201,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1294,4 +1338,838 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ข้อมูลประกอบข้อเสนอพัฒนากระสอบรูปแบบใหม่</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>กระสอบมีปีกขนาดใหญ่ กรอกยากและหนักตอนขนย้าย เมื่อเทียบกับกระสอบบังเกอร์และ Flex MSE (น้ำหนักคิดจากทรายหลวมแห้ง ค่าจากแผ่น "เปรียบเทียบ")</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>1. น้ำหนักที่ต้องยก</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>กระสอบมีปีก (GGS)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>กระสอบบังเกอร์ทหาร</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Flex MSE</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>ที่มา / สถานะ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>น้ำหนักต่อใบ ค่ากลาง (กก.)</t>
+        </is>
+      </c>
+      <c r="B6" s="13">
+        <f>'เปรียบเทียบ'!B20</f>
+        <v/>
+      </c>
+      <c r="C6" s="13">
+        <f>'เปรียบเทียบ'!C20</f>
+        <v/>
+      </c>
+      <c r="D6" s="13">
+        <f>'เปรียบเทียบ'!D20</f>
+        <v/>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>คำนวณจากแผ่น "เปรียบเทียบ" (ยังไม่ได้ชั่งจริง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>น้ำหนักต่อคนที่ยก (กก.)</t>
+        </is>
+      </c>
+      <c r="B7" s="13">
+        <f>B6/B15</f>
+        <v/>
+      </c>
+      <c r="C7" s="13">
+        <f>C6/C15</f>
+        <v/>
+      </c>
+      <c r="D7" s="13">
+        <f>D6/D15</f>
+        <v/>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>หารด้วยจำนวนคนยกต่อใบ (แถวที่ 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>เทียบ load constant NIOSH 23 กก. (เท่า)</t>
+        </is>
+      </c>
+      <c r="B8" s="13">
+        <f>B6/23</f>
+        <v/>
+      </c>
+      <c r="C8" s="13">
+        <f>C6/23</f>
+        <v/>
+      </c>
+      <c r="D8" s="13">
+        <f>D6/23</f>
+        <v/>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>NIOSH ใช้ 23 กก. เป็นค่าสูงสุดในสภาพยกเหมาะสมที่สุด (CCOHS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>เทียบเกณฑ์ ILO 55 กก. ต่อคน (เท่า)</t>
+        </is>
+      </c>
+      <c r="B9" s="13">
+        <f>B6/55</f>
+        <v/>
+      </c>
+      <c r="C9" s="13">
+        <f>C6/55</f>
+        <v/>
+      </c>
+      <c r="D9" s="13">
+        <f>D6/55</f>
+        <v/>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>ILO R128 ผู้ชายผู้ใหญ่ยกคนเดียวไม่ควรเกิน 55 กก. (ยังไม่ได้ตรวจกฎหมายไทย)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>ผลเทียบเกณฑ์ NIOSH 23 กก. (คนเดียว)</t>
+        </is>
+      </c>
+      <c r="B10" s="21">
+        <f>IF(B6&lt;=23,"ไม่เกิน","เกิน")&amp;" ("&amp;TEXT(B6/23,"0.0")&amp;" เท่า)"</f>
+        <v/>
+      </c>
+      <c r="C10" s="21">
+        <f>IF(C6&lt;=23,"ไม่เกิน","เกิน")&amp;" ("&amp;TEXT(C6/23,"0.0")&amp;" เท่า)"</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
+        <f>IF(D6&lt;=23,"ไม่เกิน","เกิน")&amp;" ("&amp;TEXT(D6/23,"0.0")&amp;" เท่า)"</f>
+        <v/>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>เกินเกณฑ์ หมายถึงต้องยก 2 คนหรือใช้เครื่องช่วย</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2. การกรอกและการยก</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>กระสอบมีปีก (GGS)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>กระสอบบังเกอร์ทหาร</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Flex MSE</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>ที่มา / สถานะ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>ขนาดผ้าก่อนกรอก</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>1.50 x 0.75 ม.</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>0.75 x 0.35 ม.</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>0.89 x 0.38 ม.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>แบบ 690044 CE / หน้าร้าน / datasheet Flex MSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>จำนวนคนยกต่อใบ</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>ผู้ใช้แจ้งว่ามีปีกต้อง 2 คน / ผู้ผลิต Flex ระบุ 2 คน / บังเกอร์ประมาณ 1 คน</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>ช่องทางที่ทรายลงถุง (ม.)</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>มีปีก: คอแคบของปีกบนตามแบบ / บังเกอร์: ปากถุง / Flex: ช่องแม่แบบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>ช่องทางทราย เทียบความกว้างที่ต้องเติม</t>
+        </is>
+      </c>
+      <c r="B17" s="16">
+        <f>B16/0.75</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f>C16/0.31</f>
+        <v/>
+      </c>
+      <c r="D17" s="16">
+        <f>D16/0.3</f>
+        <v/>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>ช่องหารด้วยความกว้างส่วนที่ต้องเติม (0.75 / 0.31 / 0.30 ม.) ยิ่งต่ำยิ่งต้องดันทรายออกข้าง</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ลักษณะปาก</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>กรวยผ้าอ่อน กว้างบน แคบล่าง ปล่อยมือแล้วหุบ</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>ปากกว้าง ตั้งตรงได้</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>ปากถุงแขวนในแม่แบบ</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>แบบกระสอบมีปีก / ภาพหน้างาน / คลิป Flex MSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>ต้องดันหรือขย้ำทรายออกข้างหรือไม่</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>ต้อง ซ้ำหลายรอบ</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>ไม่ต้อง</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>ไม่ต้อง (กวาดเข้าช่อง)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>คำบอกเล่าของผู้ใช้ + รูปทรงตามแบบ (ยังไม่ได้จับเวลา)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ขนาดหลังกรอกสม่ำเสมอหรือไม่</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>ไม่แน่นอน ขึ้นกับการดันทราย</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>สม่ำเสมอ</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>สม่ำเสมอ (ขั้นต่ำ 32 ลิตร)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>คำบอกเล่าของผู้ใช้ / คลิป Flex MSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>3. ภาระงานต่อไซต์ (ทรายเท่ากับกระสอบมีปีก 1,000 ใบ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>กระสอบมีปีก (GGS)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>กระสอบบังเกอร์ทหาร</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Flex MSE</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>ที่มา / สถานะ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>ปริมาตรทรายรวม (ลบ.ม.)</t>
+        </is>
+      </c>
+      <c r="B24" s="13">
+        <f>1000*'เปรียบเทียบ'!$B$16/1000</f>
+        <v/>
+      </c>
+      <c r="C24" s="13">
+        <f>1000*'เปรียบเทียบ'!$B$16/1000</f>
+        <v/>
+      </c>
+      <c r="D24" s="13">
+        <f>1000*'เปรียบเทียบ'!$B$16/1000</f>
+        <v/>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>1,000 ใบ x ทรายต่อใบของกระสอบมีปีก (ไฟล์คำนวณทราย)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>จำนวนกระสอบที่ต้องกรอก (ใบ)</t>
+        </is>
+      </c>
+      <c r="B25" s="22">
+        <f>B24*1000/AVERAGE('เปรียบเทียบ'!B16:'เปรียบเทียบ'!B17)</f>
+        <v/>
+      </c>
+      <c r="C25" s="22">
+        <f>C24*1000/AVERAGE('เปรียบเทียบ'!C16:'เปรียบเทียบ'!C17)</f>
+        <v/>
+      </c>
+      <c r="D25" s="22">
+        <f>D24*1000/AVERAGE('เปรียบเทียบ'!D16:'เปรียบเทียบ'!D17)</f>
+        <v/>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>หารด้วยทรายต่อใบเฉลี่ยของแต่ละแบบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>น้ำหนักทรายรวมที่ต้องขน (ตัน)</t>
+        </is>
+      </c>
+      <c r="B26" s="13">
+        <f>B25*B6/1000</f>
+        <v/>
+      </c>
+      <c r="C26" s="13">
+        <f>C25*C6/1000</f>
+        <v/>
+      </c>
+      <c r="D26" s="13">
+        <f>D25*D6/1000</f>
+        <v/>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>ทรายมวลเท่ากัน เพียงแบ่งเป็นจำนวนใบต่างกัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>จำนวนครั้งที่คนยก (ครั้ง)</t>
+        </is>
+      </c>
+      <c r="B27" s="22">
+        <f>B25*B15</f>
+        <v/>
+      </c>
+      <c r="C27" s="22">
+        <f>C25*C15</f>
+        <v/>
+      </c>
+      <c r="D27" s="22">
+        <f>D25*D15</f>
+        <v/>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>จำนวนใบ x จำนวนคนต่อใบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>น้ำหนักที่แต่ละคนยกต่อครั้ง (กก.)</t>
+        </is>
+      </c>
+      <c r="B28" s="13">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="C28" s="13">
+        <f>C7</f>
+        <v/>
+      </c>
+      <c r="D28" s="13">
+        <f>D7</f>
+        <v/>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>เบากว่าต่อครั้งแต่จำนวนครั้งเพิ่มขึ้น ต้องชั่งน้ำหนักข้อดีข้อเสียนี้</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4. การขนด้วยรถเข็น</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>กระสอบมีปีก (GGS)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>กระสอบบังเกอร์ทหาร</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Flex MSE</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>ที่มา / สถานะ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>จำนวนใบที่รถเข็นรับได้ต่อเที่ยว (ใบ)</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>มีปีก 2 ใบ: คนงานแจ้ง / บังเกอร์ 7 และ Flex 4: ใช้ในอนิเมชั่นเทียบ ยังไม่ได้ทดลองจริง</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>น้ำหนักทรายต่อเที่ยว (กก.)</t>
+        </is>
+      </c>
+      <c r="B33" s="23">
+        <f>B32*B6</f>
+        <v/>
+      </c>
+      <c r="C33" s="23">
+        <f>C32*C6</f>
+        <v/>
+      </c>
+      <c r="D33" s="23">
+        <f>D32*D6</f>
+        <v/>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>จำนวนใบ x น้ำหนักต่อใบ (ไม่รวมตัวรถเข็นและถุง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>ความสูงกองบนรถเข็น (ม.)</t>
+        </is>
+      </c>
+      <c r="B34" s="15">
+        <f>B32*0.2</f>
+        <v/>
+      </c>
+      <c r="C34" s="15">
+        <f>ROUNDUP(C32/2,0)*0.13</f>
+        <v/>
+      </c>
+      <c r="D34" s="15">
+        <f>ROUNDUP(D32/2,0)*0.14</f>
+        <v/>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>ประมาณจากความหนาหลังกรอก มีปีกซ้อน 2 ชั้น / บังเกอร์และ Flex เรียง 2 ใบต่อชั้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>5. ข้อเสนอเกณฑ์ออกแบบกระสอบรูปแบบใหม่ (เบื้องต้น)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>ค่าเสนอ</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>เหตุผลจากข้อมูลข้างบน</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>สถานะ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>น้ำหนักกรอกเต็มต่อใบ (กก.)</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>ให้คนเดียวยกได้ ใกล้เกณฑ์ NIOSH 23 กก. กระสอบมีปีกปัจจุบัน ~79 กก. เกินราว 3.4 เท่า</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="n"/>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>ข้อเสนอ ต้องยืนยันหน้างาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ทรายต่อใบที่สอดคล้อง (ลิตร)</t>
+        </is>
+      </c>
+      <c r="B39" s="13">
+        <f>B38/'เปรียบเทียบ'!B4*1000</f>
+        <v/>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>น้ำหนักเสนอหารด้วยความหนาแน่นสูงสุด (ช่อง B4 แผ่นแรก)</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>คำนวณ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>ความกว้างปากหรือช่องกรอก (ม.)</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>เท่ากระสอบบังเกอร์ที่กางค้างได้เอง ปัจจุบันคอของกระสอบมีปีกแคบ 0.19 ม.</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="n"/>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>ข้อเสนอ ต้องทดลองกรอกจริง</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>จำนวนคนที่ต้องใช้กรอก</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>1–2 คน</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>ลดจาก 2 คนตลอด เพราะปากไม่ต้องมีคนจับค้างไว้</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="n"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>ข้อเสนอ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>ปีกข้างและปีกบน</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>คงไว้ตามหน้าที่ยึดชั้นและกันดินหลุด</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>ปีกให้กระสอบชั้นบนทับชั้นล่าง ตัวถุงเล็กลงได้โดยเรียงชั้นถี่ขึ้น</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="n"/>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>ต้องตรวจกับวิศวกรผู้ออกแบบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>6. ข้อมูลหน้างานที่ควรเก็บเพิ่มให้ข้อเสนอหนักแน่น (ตัวเลขข้างบนยังเป็นค่าคำนวณ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>1. ชั่งกระสอบมีปีกที่กรอกจริง 5–10 ใบ (กก.) เทียบกับ ~79 กก. ที่คำนวณ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2. จับเวลากรอก 1 ใบ (นาที) และจดจำนวนคนที่ใช้ เทียบกับกระสอบบังเกอร์ถ้ามี</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>3. วัดขนาดหลังกรอก ยาว x กว้าง x หนา ของกระสอบมีปีก 5 ใบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>4. นับจำนวนใบต่อวัน จำนวนเที่ยวรถเข็น และบันทึกปัญหา (รถเข็นล้ม ทรายหก คนปวดหลัง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>5. ถ่ายวิดีโอการกรอกและขนเป็นหลักฐานประกอบข้อเสนอ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>แหล่งอ้างอิงเกณฑ์ยก: NIOSH load constant 23 กก. (CCOHS, ccohs.gc.ca/oshanswers/ergonomics/niosh) และ ILO R128 ผู้ชายผู้ใหญ่ไม่เกิน 55 กก. (training.itcilo.org/actrav_cdrom2/en/osh/legis/r128.htm) เกณฑ์ตามกฎหมายแรงงานไทยยังไม่ได้ตรวจ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C39:D39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>